--- a/data/trans_orig/P02E$contratada-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007 (tasa de respuesta: 96,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96183</t>
+          <t>95502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108017</t>
+          <t>107741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230453</t>
+          <t>231754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252222</t>
+          <t>253259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>332496</t>
+          <t>332967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>357160</t>
+          <t>356971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35818</t>
+          <t>36265</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20609</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>347209</t>
+          <t>347435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>368849</t>
+          <t>369317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512257</t>
+          <t>511894</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>536920</t>
+          <t>536321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>867457</t>
+          <t>869206</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>900440</t>
+          <t>901413</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24893</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47984</t>
+          <t>46498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,47 +1464,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>55763</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>41865</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>69390</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>55763</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>42543</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>72264</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>88800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107217</t>
+          <t>106920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144803</t>
+          <t>144845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159093</t>
+          <t>159261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239162</t>
+          <t>240483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262201</t>
+          <t>262076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>43844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -1983,97 +1983,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5089</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5111</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>546033</t>
+          <t>542866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>577409</t>
+          <t>575356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>902148</t>
+          <t>904399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>938991</t>
+          <t>938538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1458464</t>
+          <t>1459284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1506307</t>
+          <t>1507798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93071</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>134030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145610</t>
+          <t>145399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164939</t>
+          <t>165014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334013</t>
+          <t>335420</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>358951</t>
+          <t>359885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486837</t>
+          <t>486838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518434</t>
+          <t>517984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,47 +3028,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20856</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>31019</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>3,48%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20856</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13295</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31570</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46875</t>
+          <t>46873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18138</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>573115</t>
+          <t>574201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>596644</t>
+          <t>597145</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>827794</t>
+          <t>827868</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>857251</t>
+          <t>858546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1408834</t>
+          <t>1409194</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1446778</t>
+          <t>1448086</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40918</t>
+          <t>40659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59297</t>
+          <t>58783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59986</t>
+          <t>58781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93299</t>
+          <t>91440</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145711</t>
+          <t>145172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>163762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187591</t>
+          <t>187202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207699</t>
+          <t>207652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338884</t>
+          <t>341088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366702</t>
+          <t>367112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23343</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>35332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60461</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>880169</t>
+          <t>879692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>916169</t>
+          <t>916451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1366090</t>
+          <t>1367614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1411974</t>
+          <t>1410901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2260191</t>
+          <t>2263334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2316795</t>
+          <t>2315387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37728</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67043</t>
+          <t>67543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>98066</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108595</t>
+          <t>110305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154466</t>
+          <t>155878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>25877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>48320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016 (tasa de respuesta: 93,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102001</t>
+          <t>102178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116872</t>
+          <t>117092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166737</t>
+          <t>166485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185070</t>
+          <t>185047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275661</t>
+          <t>274288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>298554</t>
+          <t>298219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>432101</t>
+          <t>433568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>455265</t>
+          <t>455402</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>601148</t>
+          <t>602494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>634556</t>
+          <t>635616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1043956</t>
+          <t>1044080</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1083430</t>
+          <t>1085213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30605</t>
+          <t>30155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47971</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80023</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66618</t>
+          <t>65066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100528</t>
+          <t>100107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>25070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122265</t>
+          <t>122044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136871</t>
+          <t>137126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163659</t>
+          <t>163312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186067</t>
+          <t>187045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>291981</t>
+          <t>290910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320379</t>
+          <t>319388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18573</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -6093,97 +6093,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27992</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29224</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54368</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>670770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700613</t>
+          <t>700302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>948471</t>
+          <t>948866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>993358</t>
+          <t>992708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1630247</t>
+          <t>1631918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1684476</t>
+          <t>1684104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29064</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54024</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86382</t>
+          <t>85956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126047</t>
+          <t>126572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122969</t>
+          <t>122457</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>167309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32317</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P02E$contratada-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95502</t>
+          <t>97068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107741</t>
+          <t>107976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231754</t>
+          <t>231514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253259</t>
+          <t>251652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>332967</t>
+          <t>333768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356971</t>
+          <t>356850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36265</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>347435</t>
+          <t>346377</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>369317</t>
+          <t>368695</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511894</t>
+          <t>510863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>536321</t>
+          <t>536433</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>869206</t>
+          <t>865995</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>901413</t>
+          <t>899030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46498</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41865</t>
+          <t>42792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69390</t>
+          <t>72101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88800</t>
+          <t>88830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106920</t>
+          <t>107197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144845</t>
+          <t>143818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159261</t>
+          <t>159207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>240483</t>
+          <t>238152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262076</t>
+          <t>262564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>22775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43844</t>
+          <t>44764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>542866</t>
+          <t>545566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>575356</t>
+          <t>576200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>904399</t>
+          <t>903129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>938538</t>
+          <t>938878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1459284</t>
+          <t>1458314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1507798</t>
+          <t>1506480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77764</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92870</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134030</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145399</t>
+          <t>145161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165014</t>
+          <t>164735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335420</t>
+          <t>332087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>359885</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486838</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>517984</t>
+          <t>517934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46873</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>30148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,47 +3293,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>13005</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>7084</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>22988</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>13005</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>7085</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>22702</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>574201</t>
+          <t>573637</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>597145</t>
+          <t>596290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>827868</t>
+          <t>826242</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>858546</t>
+          <t>857795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1409194</t>
+          <t>1409206</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1448086</t>
+          <t>1448808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40659</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58783</t>
+          <t>59747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58781</t>
+          <t>59429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>92226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145172</t>
+          <t>145294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163762</t>
+          <t>164445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187202</t>
+          <t>187908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207652</t>
+          <t>208304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341088</t>
+          <t>341962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367112</t>
+          <t>368100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35332</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>62350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>879692</t>
+          <t>879246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>916451</t>
+          <t>915628</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1367614</t>
+          <t>1366515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1410901</t>
+          <t>1409518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2263334</t>
+          <t>2259598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2315387</t>
+          <t>2317032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67543</t>
+          <t>67508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>63874</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>110305</t>
+          <t>111724</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155878</t>
+          <t>157161</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25877</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>25432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102178</t>
+          <t>100732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117092</t>
+          <t>116781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166485</t>
+          <t>166915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185047</t>
+          <t>185440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274288</t>
+          <t>274486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>298219</t>
+          <t>298817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>35686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29486</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>433568</t>
+          <t>433800</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>455402</t>
+          <t>455484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>602494</t>
+          <t>602055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>635616</t>
+          <t>635907</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1044080</t>
+          <t>1041308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1085213</t>
+          <t>1083671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>66660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100107</t>
+          <t>101057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>22814</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122044</t>
+          <t>122544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137126</t>
+          <t>137105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163312</t>
+          <t>162726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187045</t>
+          <t>186968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290910</t>
+          <t>290392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>319388</t>
+          <t>319864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38437</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>51398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33967</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>28385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53971</t>
+          <t>54078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670770</t>
+          <t>670040</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>700302</t>
+          <t>701710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>948866</t>
+          <t>950170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>992708</t>
+          <t>993894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1631918</t>
+          <t>1631525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1684104</t>
+          <t>1685487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85956</t>
+          <t>85168</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126572</t>
+          <t>125318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122457</t>
+          <t>123156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167309</t>
+          <t>168541</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6564,82 +6564,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10536</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19009</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>20975</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>13275</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>32237</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>10536</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5455</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>18498</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>20975</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>13223</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>31955</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
